--- a/test/Extract Thermo-calc Results-T0/Al-Cu-Li_COST/t_zero.xlsx
+++ b/test/Extract Thermo-calc Results-T0/Al-Cu-Li_COST/t_zero.xlsx
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>934.12604557</v>
+        <v>934.12622477</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1046,7 +1046,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D45">
-        <v>930.40159117</v>
+        <v>930.9474983699999</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1060,7 +1060,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D46">
-        <v>926.70713997</v>
+        <v>927.80113037</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1074,7 +1074,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D47">
-        <v>923.04197517</v>
+        <v>924.68701837</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1088,7 +1088,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D48">
-        <v>919.40676237</v>
+        <v>921.60669837</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1102,7 +1102,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D49">
-        <v>915.80196237</v>
+        <v>918.55822477</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1116,7 +1116,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D50">
-        <v>912.22673037</v>
+        <v>915.54338957</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1130,7 +1130,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D51">
-        <v>908.68196237</v>
+        <v>912.5629351699999</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1144,7 +1144,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D52">
-        <v>905.16883597</v>
+        <v>909.61529997</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D53">
-        <v>901.68401037</v>
+        <v>906.70299277</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1172,7 +1172,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D54">
-        <v>898.23205517</v>
+        <v>903.82299277</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1186,7 +1186,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D55">
-        <v>894.80882317</v>
+        <v>900.9761191699999</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1200,7 +1200,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D56">
-        <v>891.41874317</v>
+        <v>898.16416397</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1214,7 +1214,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D57">
-        <v>888.0586151700001</v>
+        <v>895.38707597</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1228,7 +1228,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D58">
-        <v>884.72869517</v>
+        <v>892.64480397</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1242,7 +1242,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D59">
-        <v>881.4317479699999</v>
+        <v>889.9368359699999</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1256,7 +1256,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D60">
-        <v>878.16582797</v>
+        <v>887.2622503699999</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1270,7 +1270,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D61">
-        <v>874.9312423699999</v>
+        <v>884.62417037</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D62">
-        <v>871.72727437</v>
+        <v>882.02080397</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1298,7 +1298,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D63">
-        <v>868.55735437</v>
+        <v>879.45396877</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D64">
-        <v>865.41815437</v>
+        <v>876.92200077</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1326,7 +1326,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D65">
-        <v>862.3122343700001</v>
+        <v>874.42427277</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1340,7 +1340,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D66">
-        <v>859.23928717</v>
+        <v>871.96463757</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1354,7 +1354,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D67">
-        <v>856.19736717</v>
+        <v>869.53986957</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1368,7 +1368,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D68">
-        <v>853.18867597</v>
+        <v>867.15183757</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1382,7 +1382,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D69">
-        <v>850.21344397</v>
+        <v>864.80194957</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1396,7 +1396,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D70">
-        <v>847.2726695699999</v>
+        <v>862.48718477</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1410,7 +1410,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D71">
-        <v>844.36302477</v>
+        <v>860.20877197</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D72">
-        <v>841.48911757</v>
+        <v>857.97049997</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1438,7 +1438,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D73">
-        <v>838.64756877</v>
+        <v>855.76653197</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1452,7 +1452,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D74">
-        <v>835.84073357</v>
+        <v>853.6017319699999</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1466,7 +1466,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D75">
-        <v>833.06876557</v>
+        <v>851.47584397</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1480,7 +1480,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D76">
-        <v>830.33181837</v>
+        <v>849.3878439699999</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1494,7 +1494,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D77">
-        <v>827.62876557</v>
+        <v>847.33855117</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1508,7 +1508,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D78">
-        <v>824.96073357</v>
+        <v>845.32658317</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1522,7 +1522,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D79">
-        <v>822.32838797</v>
+        <v>843.35462797</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1536,7 +1536,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D80">
-        <v>819.73011597</v>
+        <v>841.42265997</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1550,7 +1550,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D81">
-        <v>817.16942477</v>
+        <v>839.53062797</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1564,7 +1564,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D82">
-        <v>814.64462477</v>
+        <v>837.67781517</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1578,7 +1578,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D83">
-        <v>812.15467917</v>
+        <v>835.86545037</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1592,7 +1592,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D84">
-        <v>809.70249357</v>
+        <v>834.09266317</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>933.28548237</v>
+        <v>933.28584333</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1620,7 +1620,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D86">
-        <v>929.18468237</v>
+        <v>930.24776333</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1634,7 +1634,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D87">
-        <v>925.11255437</v>
+        <v>927.24071053</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1648,7 +1648,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D88">
-        <v>921.06612877</v>
+        <v>924.26793613</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1662,7 +1662,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D89">
-        <v>917.0457639700001</v>
+        <v>921.32798093</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1676,7 +1676,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D90">
-        <v>913.05281677</v>
+        <v>918.42079373</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1690,7 +1690,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D91">
-        <v>909.08884877</v>
+        <v>915.5468865300001</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1704,7 +1704,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D92">
-        <v>905.15073677</v>
+        <v>912.70656653</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1718,7 +1718,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D93">
-        <v>901.2387367699999</v>
+        <v>909.89932173</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1732,7 +1732,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D94">
-        <v>897.35510157</v>
+        <v>907.12407693</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1746,7 +1746,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D95">
-        <v>893.49942157</v>
+        <v>904.38426253</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1760,7 +1760,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D96">
-        <v>889.67138957</v>
+        <v>901.67711373</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1774,7 +1774,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D97">
-        <v>885.86946957</v>
+        <v>899.00498573</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1788,7 +1788,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D98">
-        <v>882.09750157</v>
+        <v>896.36690573</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1802,7 +1802,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D99">
-        <v>878.35195277</v>
+        <v>893.76210573</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1816,7 +1816,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D100">
-        <v>874.63599757</v>
+        <v>891.1928129299999</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1830,7 +1830,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D101">
-        <v>870.94799757</v>
+        <v>888.65756813</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1844,7 +1844,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D102">
-        <v>867.28672397</v>
+        <v>886.1573825299999</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1858,7 +1858,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D103">
-        <v>863.65601677</v>
+        <v>883.69098893</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1872,7 +1872,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D104">
-        <v>860.05428877</v>
+        <v>881.26253453</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1886,7 +1886,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D105">
-        <v>856.48069517</v>
+        <v>878.86733453</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1900,7 +1900,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D106">
-        <v>852.93592717</v>
+        <v>876.50925453</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1914,7 +1914,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D107">
-        <v>849.42116237</v>
+        <v>874.1850689300001</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1928,7 +1928,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D108">
-        <v>845.93551757</v>
+        <v>871.89836173</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1942,7 +1942,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D109">
-        <v>842.47874957</v>
+        <v>869.64923533</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1956,7 +1956,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D110">
-        <v>839.05316237</v>
+        <v>867.43400333</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1970,7 +1970,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D111">
-        <v>835.65570957</v>
+        <v>865.25691533</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1984,7 +1984,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D112">
-        <v>832.29092237</v>
+        <v>863.11771533</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1998,7 +1998,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D113">
-        <v>828.95567757</v>
+        <v>861.01466253</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2012,7 +2012,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D114">
-        <v>825.65135757</v>
+        <v>858.94826893</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2026,7 +2026,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D115">
-        <v>822.37724557</v>
+        <v>856.92063373</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2040,7 +2040,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D116">
-        <v>819.13487757</v>
+        <v>854.93178253</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2054,7 +2054,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D117">
-        <v>815.92333197</v>
+        <v>852.97861773</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2068,7 +2068,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D118">
-        <v>812.74378637</v>
+        <v>851.06549133</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2082,7 +2082,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D119">
-        <v>809.5949607699999</v>
+        <v>849.19240333</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2096,7 +2096,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D120">
-        <v>806.47900557</v>
+        <v>847.35576973</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2110,7 +2110,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D121">
-        <v>803.39581837</v>
+        <v>845.5597377300001</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2124,7 +2124,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D122">
-        <v>800.34509197</v>
+        <v>843.80456333</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2138,7 +2138,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D123">
-        <v>797.32718477</v>
+        <v>842.08696973</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2152,7 +2152,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D124">
-        <v>794.34242957</v>
+        <v>840.4117697299999</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2166,7 +2166,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D125">
-        <v>791.39202957</v>
+        <v>838.77486733</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>931.13995149</v>
+        <v>931.13909133</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2194,7 +2194,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D127">
-        <v>926.66987149</v>
+        <v>928.22596493</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2208,7 +2208,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D128">
-        <v>922.22590349</v>
+        <v>925.34437773</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2222,7 +2222,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D129">
-        <v>917.80430989</v>
+        <v>922.49607053</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2236,7 +2236,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D130">
-        <v>913.40685709</v>
+        <v>919.68083853</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2250,7 +2250,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D131">
-        <v>909.0324442899999</v>
+        <v>916.89760653</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2264,7 +2264,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D132">
-        <v>904.68480909</v>
+        <v>914.14673293</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2278,7 +2278,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D133">
-        <v>900.3600090899999</v>
+        <v>911.42832013</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2292,7 +2292,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D134">
-        <v>896.05773709</v>
+        <v>908.74431373</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2306,7 +2306,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D135">
-        <v>891.78178189</v>
+        <v>906.09440653</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2320,7 +2320,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D136">
-        <v>887.53142669</v>
+        <v>903.47711373</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2334,7 +2334,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D137">
-        <v>883.30421389</v>
+        <v>900.89194893</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2348,7 +2348,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D138">
-        <v>879.10106509</v>
+        <v>898.34206093</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2362,7 +2362,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D139">
-        <v>874.92397709</v>
+        <v>895.82688653</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2376,7 +2376,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D140">
-        <v>870.77166989</v>
+        <v>893.34451853</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2390,7 +2390,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D141">
-        <v>866.6449626900001</v>
+        <v>890.8976833299999</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2404,7 +2404,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D142">
-        <v>862.54354829</v>
+        <v>888.4857153299999</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2418,7 +2418,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D143">
-        <v>858.46834829</v>
+        <v>886.10648973</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2432,7 +2432,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D144">
-        <v>854.4168026900001</v>
+        <v>883.76325773</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2446,7 +2446,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D145">
-        <v>850.3920346899999</v>
+        <v>881.4568897299999</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2460,7 +2460,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D146">
-        <v>846.39376269</v>
+        <v>879.18441613</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2474,7 +2474,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D147">
-        <v>842.42180749</v>
+        <v>876.94614413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2488,7 +2488,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D148">
-        <v>838.47622029</v>
+        <v>874.7461441299999</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2502,7 +2502,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D149">
-        <v>834.55654029</v>
+        <v>872.57991053</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2516,7 +2516,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D150">
-        <v>830.66450829</v>
+        <v>870.45238413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2530,7 +2530,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D151">
-        <v>826.79858829</v>
+        <v>868.35957133</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2544,7 +2544,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D152">
-        <v>822.96031629</v>
+        <v>866.30280333</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2558,7 +2558,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D153">
-        <v>819.14877069</v>
+        <v>864.28489613</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2572,7 +2572,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D154">
-        <v>815.36553869</v>
+        <v>862.30280333</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2586,7 +2586,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D155">
-        <v>811.60872589</v>
+        <v>860.35803533</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2600,7 +2600,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D156">
-        <v>807.88119949</v>
+        <v>858.45166733</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2614,7 +2614,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D157">
-        <v>804.1818330900001</v>
+        <v>856.5836993299999</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2628,7 +2628,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D158">
-        <v>800.51175309</v>
+        <v>854.75157133</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2642,7 +2642,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D159">
-        <v>796.86983309</v>
+        <v>852.96086413</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2656,7 +2656,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D160">
-        <v>793.25786509</v>
+        <v>851.20609933</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2670,7 +2670,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D161">
-        <v>789.67351949</v>
+        <v>849.49137293</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2684,7 +2684,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D162">
-        <v>786.12076429</v>
+        <v>847.81617293</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2698,7 +2698,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D163">
-        <v>782.59596429</v>
+        <v>846.18014093</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2712,7 +2712,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D164">
-        <v>779.10233229</v>
+        <v>844.58494093</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2726,7 +2726,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D165">
-        <v>775.64044429</v>
+        <v>843.0289089299999</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2740,7 +2740,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D166">
-        <v>772.20837005</v>
+        <v>841.51345293</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>927.84087693</v>
+        <v>927.84181133</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2768,7 +2768,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D168">
-        <v>923.00874893</v>
+        <v>925.03866253</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2782,7 +2782,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D169">
-        <v>918.19515533</v>
+        <v>922.2687425300001</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2796,7 +2796,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D170">
-        <v>913.40362893</v>
+        <v>919.53261453</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2810,7 +2810,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D171">
-        <v>908.63370893</v>
+        <v>916.8266945300001</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2824,7 +2824,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D172">
-        <v>903.88447373</v>
+        <v>914.15456653</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2838,7 +2838,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D173">
-        <v>899.15776653</v>
+        <v>911.51443853</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2852,7 +2852,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D174">
-        <v>894.45061773</v>
+        <v>908.90656653</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2866,7 +2866,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D175">
-        <v>889.76661133</v>
+        <v>906.33379213</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2880,7 +2880,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D176">
-        <v>885.10390413</v>
+        <v>903.79219853</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2894,7 +2894,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D177">
-        <v>880.46198413</v>
+        <v>901.28501133</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2908,7 +2908,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D178">
-        <v>875.84325773</v>
+        <v>898.81206413</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2922,7 +2922,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D179">
-        <v>871.24580493</v>
+        <v>896.37275533</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2936,7 +2936,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D180">
-        <v>866.67057293</v>
+        <v>893.96570253</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2950,7 +2950,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D181">
-        <v>862.1174081299999</v>
+        <v>891.59497613</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2964,7 +2964,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D182">
-        <v>857.58625933</v>
+        <v>889.2568641300001</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2978,7 +2978,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D183">
-        <v>853.07825293</v>
+        <v>886.95459213</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2992,7 +2992,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D184">
-        <v>848.59301773</v>
+        <v>884.68662413</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3006,7 +3006,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D185">
-        <v>844.13031053</v>
+        <v>882.45203853</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3020,7 +3020,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D186">
-        <v>839.69223053</v>
+        <v>880.25395853</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3034,7 +3034,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D187">
-        <v>835.2757569299999</v>
+        <v>878.0922305300001</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3048,7 +3048,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D188">
-        <v>830.88362893</v>
+        <v>875.9638849299999</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3062,7 +3062,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D189">
-        <v>826.5143361299999</v>
+        <v>873.8727105299999</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3076,7 +3076,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D190">
-        <v>822.16956813</v>
+        <v>871.81747853</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3090,7 +3090,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D191">
-        <v>817.84784013</v>
+        <v>869.79711373</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3104,7 +3104,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D192">
-        <v>813.5517121300001</v>
+        <v>867.81440653</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3118,7 +3118,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D193">
-        <v>809.27841933</v>
+        <v>865.86881933</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3132,7 +3132,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D194">
-        <v>805.03236493</v>
+        <v>863.95917453</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3146,7 +3146,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D195">
-        <v>800.80945293</v>
+        <v>862.08670093</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3160,7 +3160,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D196">
-        <v>796.61137293</v>
+        <v>860.25150093</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3174,7 +3174,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D197">
-        <v>792.44145293</v>
+        <v>858.45342093</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3188,7 +3188,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D198">
-        <v>788.29508493</v>
+        <v>856.69374093</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3202,7 +3202,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D199">
-        <v>784.17585293</v>
+        <v>854.9721537299999</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3216,7 +3216,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D200">
-        <v>780.0822209299999</v>
+        <v>853.28896653</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3230,7 +3230,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D201">
-        <v>776.01500813</v>
+        <v>851.64499853</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3244,7 +3244,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D202">
-        <v>771.97513613</v>
+        <v>850.04019853</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3258,7 +3258,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D203">
-        <v>767.96234893</v>
+        <v>848.47377293</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3272,7 +3272,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D204">
-        <v>763.97882253</v>
+        <v>846.94590093</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3286,7 +3286,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D205">
-        <v>760.02074253</v>
+        <v>845.45984653</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3300,7 +3300,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D206">
-        <v>756.09287053</v>
+        <v>844.01260173</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3314,7 +3314,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D207">
-        <v>752.19268493</v>
+        <v>842.60466573</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>923.51447949</v>
+        <v>923.51308173</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3342,7 +3342,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D209">
-        <v>918.32008589</v>
+        <v>920.81228173</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3356,7 +3356,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D210">
-        <v>913.14361229</v>
+        <v>918.14220173</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3370,7 +3370,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D211">
-        <v>907.98598029</v>
+        <v>915.50616973</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3384,7 +3384,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D212">
-        <v>902.84678029</v>
+        <v>912.9013697300001</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3398,7 +3398,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D213">
-        <v>897.72678029</v>
+        <v>910.32900493</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3412,7 +3412,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D214">
-        <v>892.62372749</v>
+        <v>907.78864013</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3426,7 +3426,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D215">
-        <v>887.54054029</v>
+        <v>905.28227213</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3440,7 +3440,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D216">
-        <v>882.47578509</v>
+        <v>902.80932493</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3454,7 +3454,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D217">
-        <v>877.43099789</v>
+        <v>900.36919693</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3468,7 +3468,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D218">
-        <v>872.4054106900001</v>
+        <v>897.96214413</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3482,7 +3482,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D219">
-        <v>867.39753869</v>
+        <v>895.58773133</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3496,7 +3496,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D220">
-        <v>862.4095066899999</v>
+        <v>893.24900493</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3510,7 +3510,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D221">
-        <v>857.44103309</v>
+        <v>890.94263693</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3524,7 +3524,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D222">
-        <v>852.49094029</v>
+        <v>888.6709825299999</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3538,7 +3538,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D223">
-        <v>847.56102029</v>
+        <v>886.43516813</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3552,7 +3552,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D224">
-        <v>842.65178509</v>
+        <v>884.23120013</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3566,7 +3566,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D225">
-        <v>837.76221069</v>
+        <v>882.0633281299999</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3580,7 +3580,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D226">
-        <v>832.89342349</v>
+        <v>879.93129613</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3594,7 +3594,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D227">
-        <v>828.04542349</v>
+        <v>877.83356813</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3608,7 +3608,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D228">
-        <v>823.21739149</v>
+        <v>875.77065613</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3622,7 +3622,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D229">
-        <v>818.40891789</v>
+        <v>873.74261133</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3636,7 +3636,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D230">
-        <v>813.62414989</v>
+        <v>871.75253133</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3650,7 +3650,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D231">
-        <v>808.85934989</v>
+        <v>869.79649933</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3664,7 +3664,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D232">
-        <v>804.11502989</v>
+        <v>867.87681933</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3678,7 +3678,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D233">
-        <v>799.3942618900001</v>
+        <v>865.99441293</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3692,7 +3692,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D234">
-        <v>794.69346189</v>
+        <v>864.14917773</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3706,7 +3706,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D235">
-        <v>790.0176474899999</v>
+        <v>862.33988493</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3720,7 +3720,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D236">
-        <v>785.36241549</v>
+        <v>860.56791693</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3734,7 +3734,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D237">
-        <v>780.73170829</v>
+        <v>858.83178893</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3748,7 +3748,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D238">
-        <v>776.12178829</v>
+        <v>857.13610893</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3762,7 +3762,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D239">
-        <v>771.53703309</v>
+        <v>855.47688333</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D240">
-        <v>766.97634189</v>
+        <v>853.85447053</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3790,7 +3790,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D241">
-        <v>762.43822989</v>
+        <v>852.27176333</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3804,7 +3804,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D242">
-        <v>757.9262298899999</v>
+        <v>850.72853133</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3818,7 +3818,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D243">
-        <v>753.43822989</v>
+        <v>849.2221633299999</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3832,7 +3832,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D244">
-        <v>748.97531789</v>
+        <v>847.75658893</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3846,7 +3846,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D245">
-        <v>744.53723789</v>
+        <v>846.33100173</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3860,7 +3860,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D246">
-        <v>740.1260890900001</v>
+        <v>844.94378893</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3874,7 +3874,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D247">
-        <v>735.73969549</v>
+        <v>843.59574413</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3888,7 +3888,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D248">
-        <v>731.38158733</v>
+        <v>842.28949133</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>918.25771405</v>
+        <v>918.25810573</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3916,7 +3916,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D250">
-        <v>912.70536845</v>
+        <v>915.64818573</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3930,7 +3930,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D251">
-        <v>907.16807565</v>
+        <v>913.07141773</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3944,7 +3944,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D252">
-        <v>901.64839565</v>
+        <v>910.52664973</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3958,7 +3958,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D253">
-        <v>896.14202765</v>
+        <v>908.01270413</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3972,7 +3972,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D254">
-        <v>890.65290125</v>
+        <v>905.53443213</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3986,7 +3986,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D255">
-        <v>885.17995405</v>
+        <v>903.08595853</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4000,7 +4000,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D256">
-        <v>879.72236685</v>
+        <v>900.6731713299999</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4014,7 +4014,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D257">
-        <v>874.28249485</v>
+        <v>898.29107853</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4028,7 +4028,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D258">
-        <v>868.8577268499999</v>
+        <v>895.94344333</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4042,7 +4042,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D259">
-        <v>863.44780685</v>
+        <v>893.62908813</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4056,7 +4056,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D260">
-        <v>858.05567885</v>
+        <v>891.34908813</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4070,7 +4070,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D261">
-        <v>852.68044685</v>
+        <v>889.10108813</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4084,7 +4084,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D262">
-        <v>847.32236685</v>
+        <v>886.88831373</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4098,7 +4098,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D263">
-        <v>841.9799540499999</v>
+        <v>884.70958733</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4112,7 +4112,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D264">
-        <v>836.65515405</v>
+        <v>882.56526733</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4126,7 +4126,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D265">
-        <v>831.3487860499999</v>
+        <v>880.45566093</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4140,7 +4140,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D266">
-        <v>826.05757325</v>
+        <v>878.38046093</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4154,7 +4154,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D267">
-        <v>820.78591885</v>
+        <v>876.34058893</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4168,7 +4168,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D268">
-        <v>815.53146765</v>
+        <v>874.33578893</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4182,7 +4182,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D269">
-        <v>810.29626765</v>
+        <v>872.36670093</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4196,7 +4196,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D270">
-        <v>805.07704205</v>
+        <v>870.43391373</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4210,7 +4210,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D271">
-        <v>799.87896205</v>
+        <v>868.53471373</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4224,7 +4224,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D272">
-        <v>794.69736845</v>
+        <v>866.67391373</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4238,7 +4238,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D273">
-        <v>789.53564045</v>
+        <v>864.84670093</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4252,7 +4252,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D274">
-        <v>784.39336845</v>
+        <v>863.05906573</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4266,7 +4266,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D275">
-        <v>779.27260045</v>
+        <v>861.30512013</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4280,7 +4280,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D276">
-        <v>774.16872845</v>
+        <v>859.59039373</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4294,7 +4294,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D277">
-        <v>769.08636045</v>
+        <v>857.91212173</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4308,7 +4308,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D278">
-        <v>764.02590605</v>
+        <v>856.2702017300001</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4322,7 +4322,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D279">
-        <v>758.98398605</v>
+        <v>854.66765453</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4336,7 +4336,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D280">
-        <v>753.96525965</v>
+        <v>853.10286733</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4350,7 +4350,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D281">
-        <v>748.96698765</v>
+        <v>851.57581453</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4364,7 +4364,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D282">
-        <v>743.99021965</v>
+        <v>850.0858689299999</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4378,7 +4378,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D283">
-        <v>739.03746445</v>
+        <v>848.63678093</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4392,7 +4392,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D284">
-        <v>734.10549645</v>
+        <v>847.22481293</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4406,7 +4406,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D285">
-        <v>729.1974900500001</v>
+        <v>845.85285773</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4420,7 +4420,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D286">
-        <v>724.31303565</v>
+        <v>844.52007053</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4434,7 +4434,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D287">
-        <v>719.45223565</v>
+        <v>843.22803853</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4448,7 +4448,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D288">
-        <v>714.61703565</v>
+        <v>841.97522573</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4462,7 +4462,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D289">
-        <v>709.80587917</v>
+        <v>840.76338573</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4476,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>912.15622797</v>
+        <v>912.15711629</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4490,7 +4490,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D291">
-        <v>906.24904077</v>
+        <v>909.63293069</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4504,7 +4504,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D292">
-        <v>900.35373197</v>
+        <v>907.14257549</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4518,7 +4518,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D293">
-        <v>894.47214477</v>
+        <v>904.68253069</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4532,7 +4532,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D294">
-        <v>888.60417677</v>
+        <v>902.25776269</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4546,7 +4546,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D295">
-        <v>882.74849677</v>
+        <v>899.86317709</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4560,7 +4560,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D296">
-        <v>876.90612877</v>
+        <v>897.50330509</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4574,7 +4574,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D297">
-        <v>871.0760487700001</v>
+        <v>895.17543309</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4588,7 +4588,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D298">
-        <v>865.26081677</v>
+        <v>892.88012429</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4602,7 +4602,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D299">
-        <v>859.45889677</v>
+        <v>890.61932429</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4616,7 +4616,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D300">
-        <v>853.67044237</v>
+        <v>888.39129229</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4630,7 +4630,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D301">
-        <v>847.89683597</v>
+        <v>886.19771789</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4644,7 +4644,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D302">
-        <v>842.13715597</v>
+        <v>884.0380378900001</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4658,7 +4658,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D303">
-        <v>836.39078797</v>
+        <v>881.91214989</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4672,7 +4672,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D304">
-        <v>830.65875597</v>
+        <v>879.82179469</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4686,7 +4686,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D305">
-        <v>824.94116237</v>
+        <v>877.76502669</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4700,7 +4700,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D306">
-        <v>819.23729037</v>
+        <v>875.74261389</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4714,7 +4714,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D307">
-        <v>813.54929037</v>
+        <v>873.7545818900001</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4728,7 +4728,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D308">
-        <v>807.87716237</v>
+        <v>871.80387469</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4742,7 +4742,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D309">
-        <v>802.22039437</v>
+        <v>869.88624269</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4756,7 +4756,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D310">
-        <v>796.57847437</v>
+        <v>868.00547469</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4770,7 +4770,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D311">
-        <v>790.95124877</v>
+        <v>866.15982989</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4784,7 +4784,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D312">
-        <v>785.34132877</v>
+        <v>864.35053709</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4798,7 +4798,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D313">
-        <v>779.74838157</v>
+        <v>862.57611149</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4812,7 +4812,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D314">
-        <v>774.17161357</v>
+        <v>860.83916429</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4826,7 +4826,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D315">
-        <v>768.61148557</v>
+        <v>859.13836429</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4840,7 +4840,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D316">
-        <v>763.06825357</v>
+        <v>857.47483789</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4854,7 +4854,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D317">
-        <v>757.54283917</v>
+        <v>855.84925069</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4868,7 +4868,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D318">
-        <v>752.03647117</v>
+        <v>854.25917069</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4882,7 +4882,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D319">
-        <v>746.54847117</v>
+        <v>852.70764429</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4896,7 +4896,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D320">
-        <v>741.07839117</v>
+        <v>851.19328909</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4910,7 +4910,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D321">
-        <v>735.62602637</v>
+        <v>849.71808909</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4924,7 +4924,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D322">
-        <v>730.1953191699999</v>
+        <v>848.28000909</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4938,7 +4938,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D323">
-        <v>724.7833511699999</v>
+        <v>846.88032909</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4952,7 +4952,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D324">
-        <v>719.39122317</v>
+        <v>845.52045709</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4966,7 +4966,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D325">
-        <v>714.02131597</v>
+        <v>844.19872909</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4980,7 +4980,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D326">
-        <v>708.6704039700001</v>
+        <v>842.91714189</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4994,7 +4994,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D327">
-        <v>703.34253197</v>
+        <v>841.67477389</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5008,7 +5008,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D328">
-        <v>698.03616397</v>
+        <v>840.47162509</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5022,7 +5022,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D329">
-        <v>692.75252877</v>
+        <v>839.30989709</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5036,7 +5036,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D330">
-        <v>687.49234317</v>
+        <v>838.18702221</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5050,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="D331">
-        <v>905.28415117</v>
+        <v>905.28441485</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5064,7 +5064,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D332">
-        <v>899.02335117</v>
+        <v>902.84249485</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5078,7 +5078,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D333">
-        <v>892.7705383700001</v>
+        <v>900.43257485</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5092,7 +5092,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D334">
-        <v>886.5302183699999</v>
+        <v>898.05580685</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5106,7 +5106,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D335">
-        <v>880.30013837</v>
+        <v>895.71103885</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5120,7 +5120,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D336">
-        <v>874.07886477</v>
+        <v>893.39903885</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5134,7 +5134,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D337">
-        <v>867.86977677</v>
+        <v>891.1206260500001</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5148,7 +5148,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D338">
-        <v>861.67169677</v>
+        <v>888.87375245</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5162,7 +5162,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D339">
-        <v>855.4824231699999</v>
+        <v>886.66302605</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5176,7 +5176,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D340">
-        <v>849.30676877</v>
+        <v>884.48491405</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5190,7 +5190,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D341">
-        <v>843.13889677</v>
+        <v>882.33854605</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5204,7 +5204,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D342">
-        <v>836.98454157</v>
+        <v>880.22771085</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5218,7 +5218,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D343">
-        <v>830.84022157</v>
+        <v>878.15189645</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5232,7 +5232,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D344">
-        <v>824.7081895699999</v>
+        <v>876.1087476500001</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5246,7 +5246,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D345">
-        <v>818.5874215699999</v>
+        <v>874.10087565</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5260,7 +5260,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D346">
-        <v>812.47945357</v>
+        <v>872.12892045</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5274,7 +5274,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D347">
-        <v>806.38172557</v>
+        <v>870.19080845</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5288,7 +5288,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D348">
-        <v>800.2977191700001</v>
+        <v>868.28648845</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5302,7 +5302,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D349">
-        <v>794.22559117</v>
+        <v>866.41852045</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5316,7 +5316,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D350">
-        <v>788.16800397</v>
+        <v>864.5863924499999</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5330,7 +5330,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D351">
-        <v>782.12075917</v>
+        <v>862.79036045</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5344,7 +5344,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D352">
-        <v>776.08800397</v>
+        <v>861.02863245</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5358,7 +5358,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D353">
-        <v>770.07009677</v>
+        <v>859.30417805</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5372,7 +5372,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D354">
-        <v>764.06386317</v>
+        <v>857.61617805</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5386,7 +5386,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D355">
-        <v>758.07378317</v>
+        <v>855.9642228500001</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5400,7 +5400,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D356">
-        <v>752.09701517</v>
+        <v>854.34938765</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5414,7 +5414,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D357">
-        <v>746.13509517</v>
+        <v>852.77180045</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5428,7 +5428,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D358">
-        <v>740.19032717</v>
+        <v>851.23102605</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5442,7 +5442,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D359">
-        <v>734.2583591699999</v>
+        <v>849.72875405</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5456,7 +5456,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D360">
-        <v>728.3452327700001</v>
+        <v>848.26358925</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5470,7 +5470,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D361">
-        <v>722.44603277</v>
+        <v>846.83554445</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5484,7 +5484,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D362">
-        <v>716.56444557</v>
+        <v>845.44546445</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5498,7 +5498,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D363">
-        <v>710.70057357</v>
+        <v>844.09475725</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5512,7 +5512,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D364">
-        <v>704.85533837</v>
+        <v>842.78275725</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5526,7 +5526,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D365">
-        <v>699.02730637</v>
+        <v>841.50885005</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5540,7 +5540,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D366">
-        <v>693.21801357</v>
+        <v>840.27590285</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5554,7 +5554,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D367">
-        <v>687.42792077</v>
+        <v>839.07987085</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5568,7 +5568,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D368">
-        <v>681.6580007699999</v>
+        <v>837.92551565</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5582,7 +5582,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D369">
-        <v>675.90600077</v>
+        <v>836.8099700499999</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5596,7 +5596,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D370">
-        <v>670.17724557</v>
+        <v>835.73477005</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5610,7 +5610,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D371">
-        <v>664.46834317</v>
+        <v>834.7001844500001</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="D372">
-        <v>897.70449037</v>
+        <v>897.70383245</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5638,7 +5638,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D373">
-        <v>891.09006477</v>
+        <v>895.3398644500001</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5652,7 +5652,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D374">
-        <v>884.48301197</v>
+        <v>893.00789645</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5666,7 +5666,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D375">
-        <v>877.8847399700001</v>
+        <v>890.70869645</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5680,7 +5680,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D376">
-        <v>871.2926119700001</v>
+        <v>888.44277645</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5694,7 +5694,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D377">
-        <v>864.70908557</v>
+        <v>886.21064845</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5708,7 +5708,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D378">
-        <v>858.13385357</v>
+        <v>884.01064845</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5722,7 +5722,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D379">
-        <v>851.56619917</v>
+        <v>881.84359565</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5736,7 +5736,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D380">
-        <v>845.00632717</v>
+        <v>879.71074445</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5750,7 +5750,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D381">
-        <v>838.45561997</v>
+        <v>877.61301645</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5764,7 +5764,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D382">
-        <v>831.9123879700001</v>
+        <v>875.54867085</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5778,7 +5778,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D383">
-        <v>825.37755277</v>
+        <v>873.51775885</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5792,7 +5792,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D384">
-        <v>818.8527527700001</v>
+        <v>871.52030605</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5806,7 +5806,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D385">
-        <v>812.33512077</v>
+        <v>869.56043405</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5820,7 +5820,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D386">
-        <v>805.82547597</v>
+        <v>867.63256205</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5834,7 +5834,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D387">
-        <v>799.32627597</v>
+        <v>865.74053005</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5848,7 +5848,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D388">
-        <v>792.83827597</v>
+        <v>863.88485005</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5862,7 +5862,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D389">
-        <v>786.35795597</v>
+        <v>862.06357645</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5876,7 +5876,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D390">
-        <v>779.88787597</v>
+        <v>860.27635085</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5890,7 +5890,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D391">
-        <v>773.42783117</v>
+        <v>858.52629645</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5904,7 +5904,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D392">
-        <v>766.97853837</v>
+        <v>856.81320845</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5918,7 +5918,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D393">
-        <v>760.53841037</v>
+        <v>855.1349364500001</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5932,7 +5932,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D394">
-        <v>754.11077517</v>
+        <v>853.4942452499999</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5946,7 +5946,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D395">
-        <v>747.69593997</v>
+        <v>851.88944525</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5960,7 +5960,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D396">
-        <v>741.29113997</v>
+        <v>850.32097165</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5974,7 +5974,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D397">
-        <v>734.8990119699999</v>
+        <v>848.78900365</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5988,7 +5988,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D398">
-        <v>728.51773837</v>
+        <v>847.29537165</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6002,7 +6002,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D399">
-        <v>722.15090317</v>
+        <v>845.83860365</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6016,7 +6016,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D400">
-        <v>715.79732877</v>
+        <v>844.41987725</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6030,7 +6030,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D401">
-        <v>709.45737357</v>
+        <v>843.04024205</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6044,7 +6044,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D402">
-        <v>703.13257357</v>
+        <v>841.69701005</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6058,7 +6058,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D403">
-        <v>696.82057357</v>
+        <v>840.3926900500001</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6072,7 +6072,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D404">
-        <v>690.52444557</v>
+        <v>839.12677005</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6086,7 +6086,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D405">
-        <v>684.24444557</v>
+        <v>837.90119565</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6100,7 +6100,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D406">
-        <v>677.98057357</v>
+        <v>836.71315085</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6114,7 +6114,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D407">
-        <v>671.73257357</v>
+        <v>835.56350605</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6128,7 +6128,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D408">
-        <v>665.50044557</v>
+        <v>834.45553805</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6142,7 +6142,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D409">
-        <v>659.28849037</v>
+        <v>833.38545805</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6156,7 +6156,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D410">
-        <v>653.09245837</v>
+        <v>832.35782285</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6170,7 +6170,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D411">
-        <v>646.91762317</v>
+        <v>831.36774285</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6184,7 +6184,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D412">
-        <v>640.76107917</v>
+        <v>830.41891725</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6198,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="D413">
-        <v>889.47196045</v>
+        <v>889.47038093</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6212,7 +6212,7 @@
         <v>0.004999995</v>
       </c>
       <c r="D414">
-        <v>882.50553485</v>
+        <v>887.18162573</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6226,7 +6226,7 @@
         <v>0.009999994999999999</v>
       </c>
       <c r="D415">
-        <v>875.54566285</v>
+        <v>884.92594573</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6240,7 +6240,7 @@
         <v>0.014999995</v>
       </c>
       <c r="D416">
-        <v>868.59045005</v>
+        <v>882.70323853</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6254,7 +6254,7 @@
         <v>0.019999995</v>
       </c>
       <c r="D417">
-        <v>861.6395380500001</v>
+        <v>880.51478413</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6268,7 +6268,7 @@
         <v>0.024999995</v>
       </c>
       <c r="D418">
-        <v>854.69231245</v>
+        <v>878.3579713300001</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6282,7 +6282,7 @@
         <v>0.029999995</v>
       </c>
       <c r="D419">
-        <v>847.75235725</v>
+        <v>876.23556493</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6296,7 +6296,7 @@
         <v>0.034999995</v>
       </c>
       <c r="D420">
-        <v>840.81752205</v>
+        <v>874.14756493</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6310,7 +6310,7 @@
         <v>0.039999995</v>
       </c>
       <c r="D421">
-        <v>833.8876020500001</v>
+        <v>872.09233293</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6324,7 +6324,7 @@
         <v>0.044999995</v>
       </c>
       <c r="D422">
-        <v>826.9628020500001</v>
+        <v>870.0715585299999</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6338,7 +6338,7 @@
         <v>0.049999995</v>
       </c>
       <c r="D423">
-        <v>820.04312205</v>
+        <v>868.08680333</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6352,7 +6352,7 @@
         <v>0.054999995</v>
       </c>
       <c r="D424">
-        <v>813.12835725</v>
+        <v>866.13445773</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6366,7 +6366,7 @@
         <v>0.059999995</v>
       </c>
       <c r="D425">
-        <v>806.22198925</v>
+        <v>864.21682573</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6380,7 +6380,7 @@
         <v>0.064999995</v>
       </c>
       <c r="D426">
-        <v>799.3197172500001</v>
+        <v>862.33605773</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6394,7 +6394,7 @@
         <v>0.069999995</v>
       </c>
       <c r="D427">
-        <v>792.42440845</v>
+        <v>860.48805773</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6408,7 +6408,7 @@
         <v>0.074999995</v>
       </c>
       <c r="D428">
-        <v>785.5340148499999</v>
+        <v>858.67610253</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6422,7 +6422,7 @@
         <v>0.079999995</v>
       </c>
       <c r="D429">
-        <v>778.65160845</v>
+        <v>856.90126733</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6436,7 +6436,7 @@
         <v>0.08499999499999999</v>
       </c>
       <c r="D430">
-        <v>771.77688205</v>
+        <v>855.1598145299999</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6450,7 +6450,7 @@
         <v>0.089999995</v>
       </c>
       <c r="D431">
-        <v>764.90891405</v>
+        <v>853.45594253</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6464,7 +6464,7 @@
         <v>0.094999995</v>
       </c>
       <c r="D432">
-        <v>758.04811405</v>
+        <v>851.78586253</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6478,7 +6478,7 @@
         <v>0.09999999499999999</v>
       </c>
       <c r="D433">
-        <v>751.1953012500001</v>
+        <v>850.15433613</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6492,7 +6492,7 @@
         <v>0.104999995</v>
       </c>
       <c r="D434">
-        <v>744.34965645</v>
+        <v>848.55913613</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6506,7 +6506,7 @@
         <v>0.109999995</v>
       </c>
       <c r="D435">
-        <v>737.51445645</v>
+        <v>846.99900813</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6520,7 +6520,7 @@
         <v>0.114999995</v>
       </c>
       <c r="D436">
-        <v>730.68642445</v>
+        <v>845.47646093</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6534,7 +6534,7 @@
         <v>0.119999995</v>
       </c>
       <c r="D437">
-        <v>723.86719885</v>
+        <v>843.99245453</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6548,7 +6548,7 @@
         <v>0.124999995</v>
       </c>
       <c r="D438">
-        <v>717.05954445</v>
+        <v>842.54398093</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6562,7 +6562,7 @@
         <v>0.129999995</v>
       </c>
       <c r="D439">
-        <v>710.25954445</v>
+        <v>841.13406093</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6576,7 +6576,7 @@
         <v>0.134999995</v>
       </c>
       <c r="D440">
-        <v>703.47109005</v>
+        <v>839.76046733</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6590,7 +6590,7 @@
         <v>0.139999995</v>
       </c>
       <c r="D441">
-        <v>696.69318285</v>
+        <v>838.4256321300001</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6604,7 +6604,7 @@
         <v>0.144999995</v>
       </c>
       <c r="D442">
-        <v>689.92838285</v>
+        <v>837.12950413</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6618,7 +6618,7 @@
         <v>0.149999995</v>
       </c>
       <c r="D443">
-        <v>683.17361805</v>
+        <v>835.87095693</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6632,7 +6632,7 @@
         <v>0.154999995</v>
       </c>
       <c r="D444">
-        <v>676.43134605</v>
+        <v>834.65255053</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6646,7 +6646,7 @@
         <v>0.159999995</v>
       </c>
       <c r="D445">
-        <v>669.70218125</v>
+        <v>833.47218573</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6660,7 +6660,7 @@
         <v>0.164999995</v>
       </c>
       <c r="D446">
-        <v>662.98581645</v>
+        <v>832.32991373</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6674,7 +6674,7 @@
         <v>0.169999995</v>
       </c>
       <c r="D447">
-        <v>656.28276365</v>
+        <v>831.22686093</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6688,7 +6688,7 @@
         <v>0.174999995</v>
       </c>
       <c r="D448">
-        <v>649.59476365</v>
+        <v>830.16415373</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6702,7 +6702,7 @@
         <v>0.179999995</v>
       </c>
       <c r="D449">
-        <v>642.9218164500001</v>
+        <v>829.1409217299999</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6716,7 +6716,7 @@
         <v>0.184999995</v>
       </c>
       <c r="D450">
-        <v>636.26504845</v>
+        <v>828.15903373</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6730,7 +6730,7 @@
         <v>0.189999995</v>
       </c>
       <c r="D451">
-        <v>629.62435725</v>
+        <v>827.21580173</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6744,7 +6744,7 @@
         <v>0.194999995</v>
       </c>
       <c r="D452">
-        <v>623.00112525</v>
+        <v>826.31352973</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6758,7 +6758,7 @@
         <v>0.199999995</v>
       </c>
       <c r="D453">
-        <v>616.39297677</v>
+        <v>825.45123213</v>
       </c>
     </row>
   </sheetData>
